--- a/stickers_to_import - Copy.xlsx
+++ b/stickers_to_import - Copy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fadi\Desktop\happy-helper-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84A6F14-0D4A-4D43-87FE-3BC5ECCAA8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B2A73D-BDC3-46A5-B571-F2CCEEC42F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,19 +40,19 @@
     <t>badge</t>
   </si>
   <si>
-    <t>Chopper</t>
-  </si>
-  <si>
-    <t>anime</t>
-  </si>
-  <si>
-    <t>🦌</t>
-  </si>
-  <si>
-    <t>One Piece</t>
-  </si>
-  <si>
-    <t>https://www.pinterest.com/pin/50384089576724253/</t>
+    <t>https://i.pinimg.com/736x/58/ad/54/58ad54669740fd6062fe6892920ddfc7.jpg</t>
+  </si>
+  <si>
+    <t>Stark</t>
+  </si>
+  <si>
+    <t>limited</t>
+  </si>
+  <si>
+    <t>show</t>
+  </si>
+  <si>
+    <t>house stark sigil</t>
   </si>
 </sst>
 </file>
@@ -448,8 +448,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.796875" customWidth="1"/>
     <col min="2" max="2" width="7.796875" customWidth="1"/>
@@ -459,7 +459,7 @@
     <col min="6" max="6" width="11.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -479,44 +479,33 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0.5</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:6" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{AD400600-714D-4357-AD8A-ADC535E9E13D}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F1 A2:D2 F2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F1 B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>